--- a/학점은행제_계획표.xlsx
+++ b/학점은행제_계획표.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\독학사관련\Bachelor\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nalki\Desktop\독학사 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8D1634F-F6C9-429D-A3EB-81A2AA7ECEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDFEDD5-CDF4-4A62-B182-2E2B70401D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19575" yWindow="9480" windowWidth="16575" windowHeight="11295" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -130,99 +130,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>● 매경 TEST(18점)
-접수/시험</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-26년 독학사 일정 참조
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>● 네트워크관리사2급(14점)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>접수/시험</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-26년 독학사 일정 참조</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>교양 3과목(9점)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>일반 3과목(9점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>20점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>40점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>10점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -243,17 +158,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전필: 20점
-전선: 30점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>110점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전필: 1점
-전선: 9점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -287,11 +192,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전필 1과목(3점)
-전선 3과목(9점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -343,11 +243,118 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>10과목(30점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>부족 학점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 5과목(15점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>● 매경 TEST(18점)
+접수/시험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+26년 독학사 일정 참조
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>● 산업보안관리사(10점)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>접수/시험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+26년 독학사 일정 참조</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10과목(36점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전필: 1점
+전선: 9점
+총합: 10점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전필 1과목(3점)
+전선 3과목(9점)
+총합: 12점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전필: 20점
+전선: 30점
+총합: 50점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -780,18 +787,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6D20EDD8-F358-4079-8974-FE5013ADC278}">
   <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="11.33203125" customWidth="1"/>
-    <col min="3" max="3" width="28.9140625" customWidth="1"/>
-    <col min="4" max="4" width="26.33203125" customWidth="1"/>
-    <col min="5" max="5" width="16.08203125" customWidth="1"/>
-    <col min="6" max="6" width="9.83203125" customWidth="1"/>
-    <col min="7" max="7" width="9.9140625" customWidth="1"/>
+    <col min="2" max="2" width="11.296875" customWidth="1"/>
+    <col min="3" max="3" width="28.8984375" customWidth="1"/>
+    <col min="4" max="4" width="26.296875" customWidth="1"/>
+    <col min="5" max="5" width="16.09765625" customWidth="1"/>
+    <col min="6" max="6" width="9.796875" customWidth="1"/>
+    <col min="7" max="7" width="9.8984375" customWidth="1"/>
     <col min="8" max="8" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
         <v>11</v>
       </c>
@@ -803,7 +810,7 @@
       <c r="G1" s="6"/>
       <c r="H1" s="6"/>
     </row>
-    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -823,100 +830,100 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="80" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="78" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="64" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="96" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" ht="93.6" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/학점은행제_계획표.xlsx
+++ b/학점은행제_계획표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nalki\Desktop\독학사 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDFEDD5-CDF4-4A62-B182-2E2B70401D14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859742E3-C089-4D81-BC8F-4AD3AC3B4642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
+    <workbookView xWindow="3960" yWindow="1308" windowWidth="17256" windowHeight="11520" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -63,10 +63,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>예상 과목 수</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>전적대</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -101,6 +97,44 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>20점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>60점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>50점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>140점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부족 학점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전필 1과목(3점)
+전선 3과목(9점)
+총합: 12점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -111,7 +145,35 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>정보처리기사 전필(20점)</t>
+      <t>● 매경 TEST(18점)
+접수/시험</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+26년 독학사 일정 참조</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>● 정보처리기사 전필(20점)</t>
     </r>
     <r>
       <rPr>
@@ -125,40 +187,84 @@
       <t xml:space="preserve">
 실기 접수 3월 23일~3월 26일
 실기 시험 4월 18일~5월 6일
+● </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>산업보안관리사(20점)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+접수/시험
+26년 독학사 일정 참조</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>● 독학사 1단계 교양(20점)
+5과목(접수완료)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>교양 3과목(9점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>60점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>30점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>50점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>140점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>110점</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시험 3/8(일)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+발표 3/30(월)</t>
+    </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -172,7 +278,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>독학사 2단계 전선(30점)
+      <t>● 독학사 2단계 전선(30점)
 최대 6과목</t>
     </r>
     <r>
@@ -186,175 +292,65 @@
       </rPr>
       <t xml:space="preserve">
 접수 4/21(화)~4/28(화)
-시험 5/31(일)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시험 5/31(일)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 발표 6/22(월)</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>독학사 1단계 교양(20점)
-5과목(접수완료)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시험 3/8(일)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-발표 3/30(월)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>부족 학점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 5과목(15점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>● 매경 TEST(18점)
-접수/시험</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-26년 독학사 일정 참조
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>● 산업보안관리사(10점)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>접수/시험</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-26년 독학사 일정 참조</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10과목(36점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>36점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전필: 1점
-전선: 9점
-총합: 10점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전필 1과목(3점)
-전선 3과목(9점)
-총합: 12점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전필: 20점
+    <t>전필: 40점
 전선: 30점
-총합: 50점</t>
+총합: 70점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>116점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교양 2과목(6점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 2과목(6점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8과목(24점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록 과목 수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -800,7 +796,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -824,40 +820,38 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="78" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="93.6" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>30</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.4">
@@ -865,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3" t="s">
@@ -873,37 +867,37 @@
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="93.6" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -911,19 +905,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/학점은행제_계획표.xlsx
+++ b/학점은행제_계획표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nalki\Desktop\독학사 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{859742E3-C089-4D81-BC8F-4AD3AC3B4642}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D31A730-1CB0-4122-B953-39C52AD271A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3960" yWindow="1308" windowWidth="17256" windowHeight="11520" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
+    <workbookView xWindow="384" yWindow="384" windowWidth="18276" windowHeight="10452" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -122,10 +122,6 @@
   </si>
   <si>
     <t>부족 학점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -160,6 +156,143 @@
       <t xml:space="preserve">
 26년 독학사 일정 참조</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>● 독학사 1단계 교양(20점)
+5과목(접수완료)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시험 3/8(일)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+발표 3/30(월)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>● 독학사 2단계 전선(30점)
+최대 6과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+접수 4/21(화)~4/28(화)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시험 5/31(일)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+발표 6/22(월)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전필: 40점
+전선: 30점
+총합: 70점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>26점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>116점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8과목(24점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등록 과목 수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교양 4과목(12점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>34점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -199,7 +332,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>산업보안관리사(20점)</t>
+      <t>산업보안관리사 전필(20점)</t>
     </r>
     <r>
       <rPr>
@@ -214,143 +347,6 @@
 접수/시험
 26년 독학사 일정 참조</t>
     </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>● 독학사 1단계 교양(20점)
-5과목(접수완료)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시험 3/8(일)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-발표 3/30(월)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>● 독학사 2단계 전선(30점)
-최대 6과목</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-접수 4/21(화)~4/28(화)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시험 5/31(일)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-발표 6/22(월)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>전필: 40점
-전선: 30점
-총합: 70점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>26점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>116점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>24점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>교양 2과목(6점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>일반 2과목(6점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>8과목(24점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>등록 과목 수</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -829,7 +825,7 @@
         <v>18</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="93.6" x14ac:dyDescent="0.4">
@@ -840,18 +836,18 @@
         <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.4">
@@ -863,7 +859,7 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
@@ -884,21 +880,19 @@
         <v>16</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>30</v>
-      </c>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
@@ -911,13 +905,13 @@
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>31</v>
       </c>
     </row>
   </sheetData>

--- a/학점은행제_계획표.xlsx
+++ b/학점은행제_계획표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nalki\Desktop\독학사 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D31A730-1CB0-4122-B953-39C52AD271A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C86874F-E45D-4212-9F1F-78214F1EE0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="384" yWindow="384" windowWidth="18276" windowHeight="10452" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
+    <workbookView xWindow="33540" yWindow="1275" windowWidth="16485" windowHeight="10455" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>전공</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -68,40 +68,6 @@
   </si>
   <si>
     <t>학점은행제 계획표</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>명지전문대(8점</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -210,58 +176,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>● 독학사 2단계 전선(30점)
-최대 6과목</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-접수 4/21(화)~4/28(화)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>시험 5/31(일)</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-발표 6/22(월)</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>전필: 40점
 전선: 30점
 총합: 70점</t>
@@ -288,14 +202,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>교양 4과목(12점)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>34점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -306,6 +212,58 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>● 독학사 2단계 전선(30점)
+최대 6과목</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+접수 4/21(화) ~ 4/28(화)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>시험 5/31(일)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+발표 6/22(월)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>● 정보처리기사 전필(20점)</t>
     </r>
     <r>
@@ -318,8 +276,8 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-실기 접수 3월 23일~3월 26일
-실기 시험 4월 18일~5월 6일
+접수 3/23(월) ~ 3/26(목)
+시험 4/18(토) ~ 5/6(수)
 ● </t>
     </r>
     <r>
@@ -344,9 +302,58 @@
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">
-접수/시험
 26년 독학사 일정 참조</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명지전문대(2점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>명지전문대(6점</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>8점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>32점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>교양 3과목(9점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반 1과목(3점)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,7 +449,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -457,6 +464,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -791,16 +801,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
     </row>
     <row r="2" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
@@ -822,32 +832,32 @@
         <v>4</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="93.6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" ht="78" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="4" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.4">
@@ -855,21 +865,23 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" s="1"/>
+        <v>18</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>27</v>
+      </c>
       <c r="F4" s="1" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.4">
@@ -877,41 +889,43 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="H5" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/학점은행제_계획표.xlsx
+++ b/학점은행제_계획표.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nalki\Desktop\독학사 관련\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C86874F-E45D-4212-9F1F-78214F1EE0A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC5D6A8C-CD7A-4372-B82D-F4D5DCA94117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33540" yWindow="1275" windowWidth="16485" windowHeight="10455" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
+    <workbookView xWindow="468" yWindow="1164" windowWidth="16488" windowHeight="10452" xr2:uid="{958FFD61-372E-4909-8713-4FCD8AE0888F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -91,12 +91,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>전필 1과목(3점)
-전선 3과목(9점)
-총합: 12점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -354,6 +348,12 @@
   </si>
   <si>
     <t>일반 1과목(3점)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전필 3과목(9점)
+전선 1과목(3점)
+총합: 12점</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -835,7 +835,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="78" x14ac:dyDescent="0.4">
@@ -846,18 +846,18 @@
         <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="4" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="62.4" x14ac:dyDescent="0.4">
@@ -869,19 +869,19 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="46.8" x14ac:dyDescent="0.4">
@@ -892,20 +892,20 @@
         <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2"/>
       <c r="E5" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.4">
@@ -919,13 +919,13 @@
       <c r="D6" s="2"/>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
